--- a/artfynd/A 17268-2022 artfynd.xlsx
+++ b/artfynd/A 17268-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17268-2022 artfynd.xlsx
+++ b/artfynd/A 17268-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100814240</v>
+        <v>100814152</v>
       </c>
       <c r="B2" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>332583.3830525154</v>
+        <v>332583</v>
       </c>
       <c r="R2" t="n">
-        <v>6613197.337258195</v>
+        <v>6613197</v>
       </c>
       <c r="S2" t="n">
         <v>66</v>
@@ -751,19 +746,9 @@
           <t>2022-05-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-05-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100814159</v>
+        <v>100814240</v>
       </c>
       <c r="B3" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>332583.3830525154</v>
+        <v>332583</v>
       </c>
       <c r="R3" t="n">
-        <v>6613197.337258195</v>
+        <v>6613197</v>
       </c>
       <c r="S3" t="n">
         <v>66</v>
@@ -867,19 +847,9 @@
           <t>2022-05-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-05-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100814152</v>
+        <v>100814234</v>
       </c>
       <c r="B4" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,26 +888,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -950,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>332583.3830525154</v>
+        <v>332583</v>
       </c>
       <c r="R4" t="n">
-        <v>6613197.337258195</v>
+        <v>6613197</v>
       </c>
       <c r="S4" t="n">
         <v>66</v>
@@ -983,19 +950,9 @@
           <t>2022-05-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-05-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100814234</v>
+        <v>100814159</v>
       </c>
       <c r="B5" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,28 +991,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>229497</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1068,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>332583.3830525154</v>
+        <v>332583</v>
       </c>
       <c r="R5" t="n">
-        <v>6613197.337258195</v>
+        <v>6613197</v>
       </c>
       <c r="S5" t="n">
         <v>66</v>
@@ -1101,19 +1051,9 @@
           <t>2022-05-13</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-05-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
